--- a/healthcare_forms/005_patient_informed_consent_for_medical_marijuana_treatment--healthcare_forms.xlsx
+++ b/healthcare_forms/005_patient_informed_consent_for_medical_marijuana_treatment--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -892,12 +892,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>printed_by</t>
+          <t>printed_by_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Printed By</t>
+          <t>Printed By 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -915,12 +915,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>date_signed</t>
+          <t>date_signed_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Date Signed</t>
+          <t>Date Signed 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -984,12 +984,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Name 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>date_of_birth_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Date of Birth</t>
+          <t>Date Of Birth 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>contact_information</t>
+          <t>contact_information_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Contact Information</t>
+          <t>Contact Information 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>medical_condition</t>
+          <t>medical_condition_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Medical Condition</t>
+          <t>Medical Condition 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>risks_of_use</t>
+          <t>risks_of_use_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Risks of Use</t>
+          <t>Risks Of Use 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
   <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1368,7 +1368,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>medical_condition_choices</t>
+          <t>medical_condition_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1385,7 +1385,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>medical_condition_choices</t>
+          <t>medical_condition_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1402,7 +1402,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>medical_condition_choices</t>
+          <t>medical_condition_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>medical_condition_choices</t>
+          <t>medical_condition_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1436,7 +1436,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>risks_of_use_choices</t>
+          <t>risks_of_use_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1453,7 +1453,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>risks_of_use_choices</t>
+          <t>risks_of_use_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1470,7 +1470,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>risks_of_use_choices</t>
+          <t>risks_of_use_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>risks_of_use_choices</t>
+          <t>risks_of_use_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
